--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486368_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486368_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5761</v>
+        <v>7.6882</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1017</v>
+        <v>5.1522</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4744</v>
+        <v>2.5361</v>
       </c>
       <c r="G2" t="n">
         <v>6.6882</v>
@@ -610,13 +610,13 @@
         <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4317</v>
+        <v>0.5438</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2704</v>
+        <v>-0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>0.702</v>
+        <v>0.7637</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2838</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3612</v>
+        <v>3.9359</v>
       </c>
       <c r="E3" t="n">
-        <v>0.179</v>
+        <v>1.1236</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1822</v>
+        <v>2.8123</v>
       </c>
       <c r="G3" t="n">
         <v>2.5309</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1697</v>
+        <v>0.405</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0839</v>
+        <v>-0.1394</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9142</v>
+        <v>0.5444</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.524</v>
+        <v>1.3703</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5026</v>
+        <v>-0.5639</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0266</v>
+        <v>1.9341</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2844</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3734</v>
+        <v>0.2196</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1334</v>
+        <v>-0.1947</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5067</v>
+        <v>0.4143</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5041</v>
+        <v>1.2914</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5607</v>
+        <v>-0.0199</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0648</v>
+        <v>1.3114</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0644</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4761</v>
+        <v>0.3112</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0274</v>
+        <v>-0.4867</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5513</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.1745</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5913</v>
+        <v>-0.519</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9086</v>
+        <v>-2.1753</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3173</v>
+        <v>1.6563</v>
       </c>
       <c r="G7" t="n">
         <v>0.046</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3426</v>
+        <v>0.4149</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0601</v>
+        <v>-0.2067</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2825</v>
+        <v>0.6216</v>
       </c>
       <c r="V7" t="n">
         <v>0.7602</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0775</v>
+        <v>-0.7209</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0311</v>
+        <v>-1.1098</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0464</v>
+        <v>0.389</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8120000000000001</v>
+        <v>1.491</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.216</v>
+        <v>1.5388</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.596</v>
+        <v>-0.0478</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7451</v>
+        <v>2.2482</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.1717</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.067</v>
+        <v>-0.7572</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.216</v>
+        <v>-0.6328</v>
       </c>
       <c r="O8" t="n">
-        <v>0.149</v>
+        <v>-0.1243</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0479</v>
+        <v>0.0051</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2259</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.231</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.4345</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2193</v>
+        <v>-0.9349</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7624</v>
+        <v>-0.9193</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5431</v>
+        <v>-0.0156</v>
       </c>
       <c r="G9" t="n">
-        <v>1.491</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5388</v>
+        <v>-0.216</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0478</v>
+        <v>-0.596</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2482</v>
+        <v>-0.7451</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1717</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0765</v>
+        <v>-0.7451</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7572</v>
+        <v>-0.067</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6328</v>
+        <v>-0.216</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1243</v>
+        <v>0.149</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6101</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4933</v>
+        <v>0.0946</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8784</v>
+        <v>0.0433</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3851</v>
+        <v>0.0514</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4345</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4989</v>
+        <v>-1.1178</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7018</v>
+        <v>-3.1441</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2029</v>
+        <v>2.0263</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5664</v>
+        <v>-0.1874</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0858</v>
+        <v>2.8893</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4806</v>
+        <v>-3.0766</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2532</v>
+        <v>1.2527</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2164</v>
+        <v>3.8871</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.0368</v>
+        <v>-2.6344</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6868</v>
+        <v>-1.4401</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1306</v>
+        <v>-0.9978</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5562</v>
+        <v>-0.4423</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R10" t="n">
-        <v>3.2626</v>
+        <v>3.6976</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9147</v>
+        <v>-0.2779</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5312</v>
+        <v>-0.6117</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3835</v>
+        <v>0.3338</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6071</v>
+        <v>-2.0473</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1481</v>
+        <v>-1.5267</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.459</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3605</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6234</v>
+        <v>0.1833</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4026</v>
+        <v>0.024</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2209</v>
+        <v>0.1592</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.251</v>
+        <v>-2.5132</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7533</v>
+        <v>-6.1921</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5023</v>
+        <v>3.6789</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1874</v>
+        <v>-3.5664</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8893</v>
+        <v>-1.0858</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0766</v>
+        <v>-2.4806</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2527</v>
+        <v>-4.2532</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8871</v>
+        <v>-1.2164</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6344</v>
+        <v>-3.0368</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4401</v>
+        <v>0.6868</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9978</v>
+        <v>0.1306</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4423</v>
+        <v>0.5562</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>3.6976</v>
+        <v>3.2626</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4111</v>
+        <v>0.9004</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2209</v>
+        <v>0.0409</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1902</v>
+        <v>0.8595</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.869299999999999</v>
+        <v>6.5817</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.0879</v>
+        <v>-9.375299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>15.9572</v>
+        <v>15.9571</v>
       </c>
       <c r="G13" t="n">
         <v>3.630000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>6.3871</v>
+        <v>6.387100000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-2.756999999999999</v>
@@ -1450,7 +1450,7 @@
         <v>-3.8489</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.224900000000001</v>
+        <v>-6.2249</v>
       </c>
       <c r="N13" t="n">
         <v>-7.316199999999999</v>
@@ -1468,19 +1468,19 @@
         <v>21.7507</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0877</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.689</v>
+        <v>-1.9768</v>
       </c>
       <c r="U13" t="n">
-        <v>4.7765</v>
+        <v>4.7768</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0233</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3221</v>
+        <v>2.322099999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-4.3454</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7453</v>
+        <v>5.3433</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4689</v>
+        <v>3.1337</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2764</v>
+        <v>2.2097</v>
       </c>
       <c r="G14" t="n">
         <v>5.0622</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7706</v>
+        <v>0.3686</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0649</v>
+        <v>-0.4002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8355</v>
+        <v>0.7688</v>
       </c>
       <c r="V14" t="n">
         <v>0.5649999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4927</v>
+        <v>4.2274</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1767</v>
+        <v>2.9474</v>
       </c>
       <c r="F15" t="n">
-        <v>1.316</v>
+        <v>1.2801</v>
       </c>
       <c r="G15" t="n">
         <v>0.455</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9953</v>
+        <v>0.73</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2882</v>
+        <v>0.0589</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7071</v>
+        <v>0.6711</v>
       </c>
       <c r="V15" t="n">
         <v>2.8249</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1346</v>
+        <v>1.6382</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.55</v>
+        <v>-1.103</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6846</v>
+        <v>2.7412</v>
       </c>
       <c r="G16" t="n">
         <v>1.0028</v>
@@ -1702,13 +1702,13 @@
         <v>3.0451</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.0171</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9469</v>
+        <v>-0.4999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4262</v>
+        <v>0.4828</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1279</v>
+        <v>0.0571</v>
       </c>
       <c r="E17" t="n">
         <v>-0.3888</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2609</v>
+        <v>0.4459</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4807</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0822</v>
+        <v>0.1027</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2603</v>
+        <v>0.4452</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8273</v>
+        <v>-0.5652</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7787</v>
+        <v>-2.3317</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9514</v>
+        <v>1.7665</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6375</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1473</v>
+        <v>0.1148</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0274</v>
+        <v>-0.5804</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8801</v>
+        <v>0.6952</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5649999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2804</v>
+        <v>-0.9336</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6118</v>
+        <v>-2.3883</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3314</v>
+        <v>1.4546</v>
       </c>
       <c r="G19" t="n">
         <v>0.2219</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.3725</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1714</v>
+        <v>-0.0481</v>
       </c>
       <c r="V19" t="n">
         <v>0.7395</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4908</v>
+        <v>-1.6462</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6716</v>
+        <v>-2.0068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1808</v>
+        <v>0.3606</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2684</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1251</v>
+        <v>-0.0303</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>-0.2632</v>
       </c>
       <c r="U20" t="n">
-        <v>0.053</v>
+        <v>0.2328</v>
       </c>
       <c r="V20" t="n">
         <v>-1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4098</v>
+        <v>-2.2865</v>
       </c>
       <c r="E21" t="n">
         <v>-2.3539</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0559</v>
+        <v>0.0674</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0418</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2603</v>
+        <v>-0.137</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1935</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2639</v>
+        <v>-2.682</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3648</v>
+        <v>-3.0295</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1009</v>
+        <v>0.3475</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6829</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0361</v>
+        <v>-0.4542</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9589</v>
+        <v>-0.6237</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0772</v>
+        <v>0.1694</v>
       </c>
       <c r="V22" t="n">
         <v>0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.554</v>
+        <v>-3.4961</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0578</v>
+        <v>-4.7225</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5038</v>
+        <v>1.2264</v>
       </c>
       <c r="G23" t="n">
         <v>-4.638</v>
@@ -2248,13 +2248,13 @@
         <v>2.3926</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.221</v>
+        <v>-0.1631</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1644</v>
+        <v>-0.8292</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9434</v>
+        <v>0.666</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.288</v>
+        <v>-3.7806</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8255</v>
+        <v>-3.7137</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4625</v>
+        <v>-0.0669</v>
       </c>
       <c r="G24" t="n">
         <v>0.3774</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9916</v>
+        <v>-0.4843</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8904</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1012</v>
+        <v>0.2944</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4111</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8695</v>
+        <v>-4.124200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.9573</v>
+        <v>-15.9571</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0878</v>
+        <v>11.833</v>
       </c>
       <c r="G25" t="n">
         <v>-3.629999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>19.5757</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0875</v>
+        <v>-0.3424000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.7766</v>
+        <v>-4.7769</v>
       </c>
       <c r="U25" t="n">
-        <v>3.689</v>
+        <v>4.434100000000001</v>
       </c>
       <c r="V25" t="n">
         <v>2.0233</v>
